--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeGsImport.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeGsImport.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\CQ-TZJY-0930\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9840"/>
   </bookViews>
@@ -14,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
   <si>
     <t>序号</t>
   </si>
@@ -97,6 +102,10 @@
   </si>
   <si>
     <t>对方交易员</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>限价指令</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -697,7 +706,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2">
         <v>128</v>
@@ -838,7 +847,7 @@
       <formula1>"指定价格,限价指令,市价指令"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6">
-      <formula1>"买入,卖出,正回购,逆回购"</formula1>
+      <formula1>"买入,卖出"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J5">
       <formula1>"数量,金额"</formula1>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeGsImport.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeGsImport.xlsx
@@ -836,23 +836,17 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="6">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:N1048576 O23:O1048576">
       <formula1>"公允价值变动计入当期损益,摊余成本类,公允价值变动计入其他综合收益"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E1048576 E1">
-      <formula1>"买入,卖出,申购,配股,配债,行权-回售,债转股,质押入库,质押出库,正回购,逆回购"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1 F7:F1048576">
-      <formula1>"指定价格,限价指令,市价指令"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576">
       <formula1>"买入,卖出"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J5">
       <formula1>"数量,金额"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576">
       <formula1>"限价指令,市价指令"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeGsImport.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrExchangeGsImport.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\CQ-TZJY-0930\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9840"/>
+    <workbookView windowWidth="19815" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
   <si>
     <t>序号</t>
   </si>
@@ -39,21 +34,39 @@
     <t>价格模式</t>
   </si>
   <si>
+    <t>净价价格</t>
+  </si>
+  <si>
     <t>全价价格</t>
   </si>
   <si>
     <t>收益率</t>
   </si>
   <si>
+    <t>目标类型</t>
+  </si>
+  <si>
     <t>指令数量</t>
   </si>
   <si>
     <t>指令金额</t>
   </si>
   <si>
+    <t>交易对手</t>
+  </si>
+  <si>
     <t>投资目的</t>
   </si>
   <si>
+    <t>本方交易员</t>
+  </si>
+  <si>
+    <t>对方交易员</t>
+  </si>
+  <si>
+    <t>约定号</t>
+  </si>
+  <si>
     <t>开始日期</t>
   </si>
   <si>
@@ -69,57 +82,30 @@
     <t>限价指令</t>
   </si>
   <si>
-    <t>摊余成本类</t>
+    <t>数量</t>
   </si>
   <si>
     <t>123002.SH</t>
   </si>
   <si>
     <t>204007.SH</t>
-  </si>
-  <si>
-    <t>交易对手</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>约定号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
-    <t>净价价格</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>本方交易员</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>对方交易员</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>限价指令</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="178" formatCode="0.000_ "/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,14 +118,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -147,20 +132,342 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -168,35 +475,321 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -245,7 +838,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -280,7 +873,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -483,14 +1076,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:S22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -510,7 +1103,7 @@
     <col min="19" max="19" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" s="1" customFormat="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -530,46 +1123,46 @@
         <v>5</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2">
         <v>1</v>
       </c>
@@ -580,13 +1173,13 @@
         <v>111111</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G2" s="2">
         <v>3.56</v>
@@ -600,20 +1193,17 @@
       <c r="L2" s="5">
         <v>356000</v>
       </c>
-      <c r="N2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" s="11"/>
+      <c r="O2" s="10"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-      <c r="R2" s="10">
+      <c r="R2" s="11">
         <v>43962</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="11">
         <v>43962</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>2</v>
       </c>
@@ -621,13 +1211,13 @@
         <v>10000</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G3" s="2">
         <v>70</v>
@@ -638,20 +1228,17 @@
       <c r="K3" s="4">
         <v>1000</v>
       </c>
-      <c r="N3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" s="11"/>
+      <c r="O3" s="10"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="10">
+      <c r="R3" s="11">
         <v>43962</v>
       </c>
-      <c r="S3" s="10">
+      <c r="S3" s="11">
         <v>43962</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>3</v>
       </c>
@@ -659,13 +1246,13 @@
         <v>10000</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G4" s="2">
         <v>3.56</v>
@@ -679,20 +1266,17 @@
       <c r="L4" s="5">
         <v>100000</v>
       </c>
-      <c r="N4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="O4" s="11"/>
+      <c r="O4" s="10"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
-      <c r="R4" s="10">
+      <c r="R4" s="11">
         <v>43962</v>
       </c>
-      <c r="S4" s="10">
+      <c r="S4" s="11">
         <v>43962</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>4</v>
       </c>
@@ -700,13 +1284,13 @@
         <v>10000</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2">
         <v>128</v>
@@ -726,20 +1310,17 @@
       <c r="L5" s="5">
         <v>128000</v>
       </c>
-      <c r="N5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="O5" s="11"/>
+      <c r="O5" s="10"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
-      <c r="R5" s="10">
+      <c r="R5" s="11">
         <v>43962</v>
       </c>
-      <c r="S5" s="10">
+      <c r="S5" s="11">
         <v>43962</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>5</v>
       </c>
@@ -747,13 +1328,13 @@
         <v>10000</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G6" s="2">
         <v>95</v>
@@ -761,96 +1342,96 @@
       <c r="K6" s="4">
         <v>1000</v>
       </c>
-      <c r="N6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="O6" s="11"/>
+      <c r="O6" s="10"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-      <c r="R6" s="10">
+      <c r="R6" s="11">
         <v>43962</v>
       </c>
-      <c r="S6" s="10">
+      <c r="S6" s="11">
         <v>43962</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="O7" s="11"/>
+    <row r="7" spans="15:17">
+      <c r="O7" s="10"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="O8" s="11"/>
+    <row r="8" spans="15:17">
+      <c r="O8" s="10"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="O9" s="11"/>
+    <row r="9" spans="15:17">
+      <c r="O9" s="10"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="O10" s="11"/>
+    <row r="10" spans="15:17">
+      <c r="O10" s="10"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="O11" s="11"/>
+    <row r="11" spans="15:17">
+      <c r="O11" s="10"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="O12" s="11"/>
+    <row r="12" spans="15:17">
+      <c r="O12" s="10"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="O13" s="11"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="O14" s="11"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="O15" s="11"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="O16" s="11"/>
-    </row>
-    <row r="17" spans="15:15" x14ac:dyDescent="0.15">
-      <c r="O17" s="11"/>
-    </row>
-    <row r="18" spans="15:15" x14ac:dyDescent="0.15">
-      <c r="O18" s="11"/>
-    </row>
-    <row r="19" spans="15:15" x14ac:dyDescent="0.15">
-      <c r="O19" s="11"/>
-    </row>
-    <row r="20" spans="15:15" x14ac:dyDescent="0.15">
-      <c r="O20" s="11"/>
-    </row>
-    <row r="21" spans="15:15" x14ac:dyDescent="0.15">
-      <c r="O21" s="11"/>
-    </row>
-    <row r="22" spans="15:15" x14ac:dyDescent="0.15">
-      <c r="O22" s="11"/>
+    <row r="13" spans="15:15">
+      <c r="O13" s="10"/>
+    </row>
+    <row r="14" spans="15:15">
+      <c r="O14" s="10"/>
+    </row>
+    <row r="15" spans="15:15">
+      <c r="O15" s="10"/>
+    </row>
+    <row r="16" spans="15:15">
+      <c r="O16" s="10"/>
+    </row>
+    <row r="17" spans="15:15">
+      <c r="O17" s="10"/>
+    </row>
+    <row r="18" spans="15:15">
+      <c r="O18" s="10"/>
+    </row>
+    <row r="19" spans="15:15">
+      <c r="O19" s="10"/>
+    </row>
+    <row r="20" spans="15:15">
+      <c r="O20" s="10"/>
+    </row>
+    <row r="21" spans="15:15">
+      <c r="O21" s="10"/>
+    </row>
+    <row r="22" spans="15:15">
+      <c r="O22" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:N1048576 O23:O1048576">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N113">
+      <formula1>"以收取该金融资产合同现金流量为目的,以收取该合同现金流量及出售金融资产为目的,以出售该金融资产为目的"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1 N114:N1048576 O23:O1048576">
       <formula1>"公允价值变动计入当期损益,摊余成本类,公允价值变动计入其他综合收益"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+      <formula1>"限价指令,市价指令"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
       <formula1>"买入,卖出"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J5">
       <formula1>"数量,金额"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576">
-      <formula1>"限价指令,市价指令"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>